--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         <v>1.95</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3.4</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>2.15</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="D7" t="n">
         <v>4.5</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="C9" t="n">
         <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="12">
@@ -615,10 +615,42 @@
         <v>1.95</v>
       </c>
       <c r="C12" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="D12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D13" t="n">
         <v>3.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,209 +448,225 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="C12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="C13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="n">
-        <v>3.25</v>
+      <c r="D15" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="9">

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
         <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="C9" t="n">
         <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C12" t="n">
         <v>4.33</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">
@@ -631,10 +631,10 @@
         <v>1.36</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +669,276 @@
         <v>7</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="C12" t="n">
         <v>4.33</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="C14" t="n">
         <v>3.7</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -668,276 +668,6 @@
       <c r="D15" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>jqf7smJ3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>G0IRHiWk</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiHVGBod</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4nbBt7Y9</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>b9cFuRmG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zZKrObIr</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hAFmNIXl</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QNDeLd21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>W0EiMxme</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>xbHaKGH7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>v3erq0f8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IgfnrK9E</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>nTbjsvPK</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YyTMIXGq</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="C5" t="n">
         <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="n">
         <v>3.7</v>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="C11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="D11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="C13" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="C3" t="n">
         <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="C5" t="n">
         <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="C9" t="n">
         <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -580,93 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="C10" t="n">
         <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="C3" t="n">
         <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="C4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
         <v>5.75</v>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,50 +448,496 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="C2" t="n">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.57</v>
+        <v>2.9</v>
       </c>
       <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
         <v>4.1</v>
       </c>
-      <c r="D4" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="n">
         <v>5.75</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="C2" t="n">
         <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
         <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -660,284 +660,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="C15" t="n">
         <v>3.7</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,71 +448,71 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -522,151 +522,151 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="C11" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="C12" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="C13" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="D13" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="C14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="C15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D15" t="n">
         <v>4.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
         <v>2.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.45</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
         <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="13">
@@ -631,7 +631,7 @@
         <v>2.6</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D13" t="n">
         <v>2.5</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -663,11 +663,399 @@
         <v>1.8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D15" t="n">
         <v>4.2</v>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="C9" t="n">
         <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="C27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="28">
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="29">

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,614 +448,226 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>GvBXzXxS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>QHhnaCp6</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>Iigr0hVa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>48ijbWaC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>dYh0Wjoq</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>nXtecjFI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>0zoadAUO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="C8" t="n">
         <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>EwZtLg7P</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>GnL8GDFt</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>zPi4VA0k</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>YNFDFXUn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="C12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>6yELDBaa</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>CEEHEipg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="C14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>4MWOCVE5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>SKZvN7pn</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>APpAklQ6</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>d0ReJPqB</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>0YXnLoFb</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,225 +448,225 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="C5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D5" t="n">
         <v>3.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D7" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="C9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="C10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.95</v>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="C14" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/usa/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3.1</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="C5" t="n">
         <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         <v>1.95</v>
       </c>
       <c r="C7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
         <v>2.7</v>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="D10" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="C14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="C15" t="n">
         <v>4.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
